--- a/etf_holdings/2026-09-15_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:46</t>
+          <t>2026-09-15 19:54:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.24%2380</t>
+          <t>+0.21%2385</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2380</v>
+        <v>2385</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.21%944,000</t>
+          <t>9.47%944,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.21%</t>
+          <t>9.47%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:46</t>
+          <t>2026-09-15 19:54:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.78%3310</t>
+          <t>-2.85%4430</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3310</v>
+        <v>4430</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.80%427,000</t>
+          <t>5.70%306,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.80%</t>
+          <t>5.70%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>427000</v>
+        <v>306000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:46</t>
+          <t>2026-09-15 19:54:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.55%4560</t>
+          <t>-5.89%3115</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-5.89%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4560</v>
+        <v>3115</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.72%306,000</t>
+          <t>5.59%427,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.72%</t>
+          <t>5.59%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>306000</v>
+        <v>427000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:46</t>
+          <t>2026-09-15 19:54:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.37%5345</t>
+          <t>-4.3%5115</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5345</v>
+        <v>5115</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.61%256,000</t>
+          <t>5.51%256,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.61%</t>
+          <t>5.51%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:46</t>
+          <t>2026-09-15 19:54:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.72%970</t>
+          <t>-1.96%951</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>970</v>
+        <v>951</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.96%1,248,000</t>
+          <t>4.99%1,248,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.96%</t>
+          <t>4.99%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:46</t>
+          <t>2026-09-15 19:54:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3443創意電子</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+4.58%6400</t>
+          <t>+1.98%2315</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6400</v>
+        <v>2315</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.07%155,000</t>
+          <t>4.10%421,644</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>4.10%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>155000</v>
+        <v>421644</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:46</t>
+          <t>2026-09-15 19:54:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3443創意電子</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.73%2270</t>
+          <t>-5.7%6035</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2270</v>
+        <v>6035</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.92%421,644</t>
+          <t>3.93%155,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>3.93%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>421644</v>
+        <v>155000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:46</t>
+          <t>2026-09-15 19:54:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-2.15%1365</t>
+          <t>-2.84%1370</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.54%613,000</t>
+          <t>3.53%613,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.53%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:46</t>
+          <t>2026-09-15 19:54:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.95%5820</t>
+          <t>-2.77%5440</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5820</v>
+        <v>5440</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.17%133,000</t>
+          <t>3.00%131,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>133000</v>
+        <v>131000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:46</t>
+          <t>2026-09-15 19:54:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0%5620</t>
+          <t>-8.76%5310</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-8.76%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5620</v>
+        <v>5310</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.01%131,000</t>
+          <t>2.97%133,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>2.97%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>131000</v>
+        <v>133000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:46</t>
+          <t>2026-09-15 19:54:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.7%2165</t>
+          <t>-2.29%11715</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2165</v>
+        <v>11715</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.89%325,000</t>
+          <t>2.76%56,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.76%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>325000</v>
+        <v>56000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:46</t>
+          <t>2026-09-15 19:54:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.75%11990</t>
+          <t>-1.87%1840</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>11990</v>
+        <v>1840</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.75%56,000</t>
+          <t>2.70%349,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.70%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>56000</v>
+        <v>349000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:46</t>
+          <t>2026-09-15 19:54:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.97%612</t>
+          <t>-3.27%592</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.72%1,084,000</t>
+          <t>2.70%1,084,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.70%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:46</t>
+          <t>2026-09-15 19:54:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.53%1875</t>
+          <t>+3.09%1670</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1875</v>
+        <v>1670</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.68%349,000</t>
+          <t>2.58%368,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>349000</v>
+        <v>368000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:46</t>
+          <t>2026-09-15 19:54:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0%1620</t>
+          <t>-2.56%17520</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.56%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1620</v>
+        <v>17520</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.44%368,000</t>
+          <t>2.42%32,900</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>368000</v>
+        <v>32900</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:48</t>
+          <t>2026-09-15 19:54:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-4.36%17885</t>
+          <t>-1.47%537</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>17885</v>
+        <v>537</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.43%32,900</t>
+          <t>2.30%1,019,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>32900</v>
+        <v>1019000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:48</t>
+          <t>2026-09-15 19:54:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+0.18%545</t>
+          <t>+1.28%1980</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>545</v>
+        <v>1980</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.28%1,019,000</t>
+          <t>2.04%245,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1019000</v>
+        <v>245000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:48</t>
+          <t>2026-09-15 19:54:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-9.98%5995</t>
+          <t>-6.47%2025</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-9.98%</t>
+          <t>-6.47%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5995</v>
+        <v>2025</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.97%80,000</t>
+          <t>1.92%225,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>80000</v>
+        <v>225000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:48</t>
+          <t>2026-09-15 19:54:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+4.27%1955</t>
+          <t>-2.8%2080</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+4.27%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1955</v>
+        <v>2080</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.96%245,000</t>
+          <t>1.80%206,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>245000</v>
+        <v>206000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:48</t>
+          <t>2026-09-15 19:54:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,34 +1663,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.93%2140</t>
+          <t>-1.21%1220</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2140</v>
+        <v>1220</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.81%206,000</t>
+          <t>1.80%351,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>206000</v>
+        <v>351000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:48</t>
+          <t>2026-09-15 19:54:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-7.14%1235</t>
+          <t>+2.84%1085</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-7.14%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1235</v>
+        <v>1085</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.78%351,000</t>
+          <t>1.76%386,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>351000</v>
+        <v>386000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:48</t>
+          <t>2026-09-15 19:54:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-2.31%1055</t>
+          <t>+1%6055</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>+1%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1055</v>
+        <v>6055</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.67%386,000</t>
+          <t>1.53%60,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>386000</v>
+        <v>60000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:48</t>
+          <t>2026-09-15 19:54:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-5.18%3480</t>
+          <t>-1.26%274</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.18%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3480</v>
+        <v>274</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.51%109,000</t>
+          <t>1.52%1,320,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>109000</v>
+        <v>1320000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:48</t>
+          <t>2026-09-15 19:54:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+0.18%277.5</t>
+          <t>-3.56%3255</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>277.5</v>
+        <v>3255</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.50%1,320,000</t>
+          <t>1.49%109,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1320000</v>
+        <v>109000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:48</t>
+          <t>2026-09-15 19:54:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,34 +1968,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.71%2810</t>
+          <t>-0.82%1215</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2810</v>
+        <v>1215</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.46%130,000</t>
+          <t>1.48%290,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>130000</v>
+        <v>290000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:48</t>
+          <t>2026-09-15 19:54:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,25 +2029,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-2.34%1250</t>
+          <t>-2.55%2675</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>-2.55%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1250</v>
+        <v>2675</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.46%290,000</t>
+          <t>1.46%130,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2056,11 +2056,11 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>290000</v>
+        <v>130000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:48</t>
+          <t>2026-09-15 19:54:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.11%489.5</t>
+          <t>-2.45%477.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>-2.45%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>489.5</v>
+        <v>477.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:48</t>
+          <t>2026-09-15 19:54:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-4.06%473</t>
+          <t>-1.59%465.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-4.06%</t>
+          <t>-1.59%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>473</v>
+        <v>465.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.94%485,000</t>
+          <t>0.95%485,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:48</t>
+          <t>2026-09-15 19:54:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.56%886</t>
+          <t>-1.35%874</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>886</v>
+        <v>874</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.89%246,000</t>
+          <t>0.90%246,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:48</t>
+          <t>2026-09-15 19:54:16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>3131弘塑</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.97%1020</t>
+          <t>+0.43%2320</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1020</v>
+        <v>2320</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.88%210,000</t>
+          <t>0.89%91,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>210000</v>
+        <v>91000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:49</t>
+          <t>2026-09-15 19:54:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+4.43%1415</t>
+          <t>-2.52%1355</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+4.43%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1415</v>
+        <v>1355</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:49</t>
+          <t>2026-09-15 19:54:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,25 +2395,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3131弘塑</t>
+          <t>1560中砂</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-5.49%2325</t>
+          <t>-2.39%735</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-5.49%</t>
+          <t>-2.39%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2325</v>
+        <v>735</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.86%91,000</t>
+          <t>0.86%277,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2422,11 +2422,11 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>91000</v>
+        <v>277000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:49</t>
+          <t>2026-09-15 19:54:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1560中砂</t>
+          <t>3034聯詠</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-4.68%753</t>
+          <t>-2.7%541</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-4.68%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>753</v>
+        <v>541</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.86%277,000</t>
+          <t>0.78%344,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>277000</v>
+        <v>344000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:49</t>
+          <t>2026-09-15 19:54:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3034聯詠</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.65%556</t>
+          <t>-5.34%221.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.65%</t>
+          <t>-5.34%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>556</v>
+        <v>221.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.78%344,000</t>
+          <t>0.74%791,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>344000</v>
+        <v>791000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:49</t>
+          <t>2026-09-15 19:54:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>2615萬海</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.21%234</t>
+          <t>-0.88%112</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>234</v>
+        <v>112</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.76%791,000</t>
+          <t>0.72%1,535,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>791000</v>
+        <v>1535000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:49</t>
+          <t>2026-09-15 19:54:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2615萬海</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.89%113</t>
+          <t>-3.85%2625</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>-3.85%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>113</v>
+        <v>2625</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.71%1,535,000</t>
+          <t>0.60%54,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1535000</v>
+        <v>54000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:49</t>
+          <t>2026-09-15 19:54:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-5.49%2580</t>
+          <t>-2.81%138.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-5.49%</t>
+          <t>-2.81%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2580</v>
+        <v>138.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.60%54,000</t>
+          <t>0.58%1,000,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>54000</v>
+        <v>1000000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:49</t>
+          <t>2026-09-15 19:54:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3293鈊象</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+1.42%142.5</t>
+          <t>-0.43%696</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+1.42%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>142.5</v>
+        <v>696</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.58%1,000,000</t>
+          <t>0.57%195,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1000000</v>
+        <v>195000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:49</t>
+          <t>2026-09-15 19:54:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3293鈊象</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.56%693</t>
+          <t>-4.71%972</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>-4.71%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>693</v>
+        <v>972</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.56%195,000</t>
+          <t>0.53%130,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>195000</v>
+        <v>130000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:49</t>
+          <t>2026-09-15 19:54:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>5289宜鼎</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-2.63%962</t>
+          <t>-1.16%1275</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>962</v>
+        <v>1275</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.35%88,000</t>
+          <t>0.34%63,294</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>88000</v>
+        <v>63294</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:49</t>
+          <t>2026-09-15 19:54:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-7.03%1190</t>
+          <t>+1.26%1205</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-7.03%</t>
+          <t>+1.26%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1190</v>
+        <v>1205</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.33%67,000</t>
+          <t>0.34%67,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:49</t>
+          <t>2026-09-15 19:54:18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,25 +3005,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5289宜鼎</t>
+          <t>2451創見</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.39%1295</t>
+          <t>-0.36%273</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1295</v>
+        <v>273</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.33%63,294</t>
+          <t>0.33%287,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3032,11 +3032,11 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>63294</v>
+        <v>287000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:49</t>
+          <t>2026-09-15 19:54:18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2451創見</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.9%274</t>
+          <t>-7.48%890</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-7.48%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>274</v>
+        <v>890</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.32%287,000</t>
+          <t>0.33%88,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>287000</v>
+        <v>88000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:49</t>
+          <t>2026-09-15 19:54:18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.11%402.5</t>
+          <t>-2.39%388.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>-2.39%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>402.5</v>
+        <v>388.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:49</t>
+          <t>2026-09-15 19:54:18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-3.63%1990</t>
+          <t>-0.78%1920</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-3.63%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1990</v>
+        <v>1920</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:50</t>
+          <t>2026-09-15 19:54:19</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,18 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+1.28%713</t>
+          <t>-1.4%703</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+1.28%</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
+          <t>-1.4%</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>703</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3282,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3299,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:50</t>
+          <t>2026-09-15 19:54:19</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3317,18 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+2.28%539</t>
+          <t>-0.37%537</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+2.28%</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
+          <t>-0.37%</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>537</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3345,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3362,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:50</t>
+          <t>2026-09-15 19:54:19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3380,27 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-6.71%160</t>
+          <t>-0.31%159.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-6.71%</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+          <t>-0.31%</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>159.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.13%203,000</t>
+          <t>0.14%203,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3408,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3425,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:50</t>
+          <t>2026-09-15 19:54:19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3443,27 +3437,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-1.17%1270</t>
+          <t>+0.79%1280</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-1.17%</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
+          <t>+0.79%</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1280</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.07%14,000</t>
+          <t>0.08%14,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3471,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3488,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:50</t>
+          <t>2026-09-15 19:54:19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3506,18 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+1.42%142.5</t>
+          <t>+0.7%143.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+1.42%</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>142.5</t>
-        </is>
+          <t>+0.7%</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>143.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-15_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:15</t>
+          <t>2026-09-15 21:13:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:15</t>
+          <t>2026-09-15 21:13:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:15</t>
+          <t>2026-09-15 21:13:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:15</t>
+          <t>2026-09-15 21:13:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:15</t>
+          <t>2026-09-15 21:13:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:15</t>
+          <t>2026-09-15 21:13:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:15</t>
+          <t>2026-09-15 21:13:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:15</t>
+          <t>2026-09-15 21:13:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:15</t>
+          <t>2026-09-15 21:13:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:15</t>
+          <t>2026-09-15 21:13:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:15</t>
+          <t>2026-09-15 21:13:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:15</t>
+          <t>2026-09-15 21:13:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:15</t>
+          <t>2026-09-15 21:13:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:15</t>
+          <t>2026-09-15 21:13:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:15</t>
+          <t>2026-09-15 21:13:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:16</t>
+          <t>2026-09-15 21:13:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:16</t>
+          <t>2026-09-15 21:13:12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:16</t>
+          <t>2026-09-15 21:13:12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:16</t>
+          <t>2026-09-15 21:13:12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:16</t>
+          <t>2026-09-15 21:13:12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:16</t>
+          <t>2026-09-15 21:13:12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:16</t>
+          <t>2026-09-15 21:13:12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:16</t>
+          <t>2026-09-15 21:13:12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:16</t>
+          <t>2026-09-15 21:13:12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:16</t>
+          <t>2026-09-15 21:13:12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:16</t>
+          <t>2026-09-15 21:13:12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:16</t>
+          <t>2026-09-15 21:13:12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:16</t>
+          <t>2026-09-15 21:13:12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:16</t>
+          <t>2026-09-15 21:13:12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:16</t>
+          <t>2026-09-15 21:13:12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:18</t>
+          <t>2026-09-15 21:13:13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:18</t>
+          <t>2026-09-15 21:13:13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:18</t>
+          <t>2026-09-15 21:13:13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:18</t>
+          <t>2026-09-15 21:13:13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:18</t>
+          <t>2026-09-15 21:13:13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:18</t>
+          <t>2026-09-15 21:13:13</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:18</t>
+          <t>2026-09-15 21:13:13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:18</t>
+          <t>2026-09-15 21:13:13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:18</t>
+          <t>2026-09-15 21:13:13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:18</t>
+          <t>2026-09-15 21:13:13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:18</t>
+          <t>2026-09-15 21:13:13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:18</t>
+          <t>2026-09-15 21:13:13</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:18</t>
+          <t>2026-09-15 21:13:13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:18</t>
+          <t>2026-09-15 21:13:13</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:18</t>
+          <t>2026-09-15 21:13:13</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:19</t>
+          <t>2026-09-15 21:13:14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:19</t>
+          <t>2026-09-15 21:13:14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:19</t>
+          <t>2026-09-15 21:13:14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:19</t>
+          <t>2026-09-15 21:13:14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:19</t>
+          <t>2026-09-15 21:13:14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-15_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:10</t>
+          <t>2026-09-15 22:23:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:10</t>
+          <t>2026-09-15 22:23:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:10</t>
+          <t>2026-09-15 22:23:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:10</t>
+          <t>2026-09-15 22:23:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:10</t>
+          <t>2026-09-15 22:23:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:10</t>
+          <t>2026-09-15 22:23:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:10</t>
+          <t>2026-09-15 22:23:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:10</t>
+          <t>2026-09-15 22:23:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:10</t>
+          <t>2026-09-15 22:23:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:10</t>
+          <t>2026-09-15 22:23:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:10</t>
+          <t>2026-09-15 22:23:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:10</t>
+          <t>2026-09-15 22:23:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:10</t>
+          <t>2026-09-15 22:23:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:10</t>
+          <t>2026-09-15 22:23:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:10</t>
+          <t>2026-09-15 22:23:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:12</t>
+          <t>2026-09-15 22:23:29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:12</t>
+          <t>2026-09-15 22:23:29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:12</t>
+          <t>2026-09-15 22:23:29</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:12</t>
+          <t>2026-09-15 22:23:29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:12</t>
+          <t>2026-09-15 22:23:29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:12</t>
+          <t>2026-09-15 22:23:29</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:12</t>
+          <t>2026-09-15 22:23:29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:12</t>
+          <t>2026-09-15 22:23:29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:12</t>
+          <t>2026-09-15 22:23:29</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:12</t>
+          <t>2026-09-15 22:23:29</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:12</t>
+          <t>2026-09-15 22:23:29</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:12</t>
+          <t>2026-09-15 22:23:29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:12</t>
+          <t>2026-09-15 22:23:29</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:12</t>
+          <t>2026-09-15 22:23:29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:12</t>
+          <t>2026-09-15 22:23:29</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:13</t>
+          <t>2026-09-15 22:23:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:13</t>
+          <t>2026-09-15 22:23:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:13</t>
+          <t>2026-09-15 22:23:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:13</t>
+          <t>2026-09-15 22:23:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:13</t>
+          <t>2026-09-15 22:23:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:13</t>
+          <t>2026-09-15 22:23:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:13</t>
+          <t>2026-09-15 22:23:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:13</t>
+          <t>2026-09-15 22:23:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:13</t>
+          <t>2026-09-15 22:23:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:13</t>
+          <t>2026-09-15 22:23:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:13</t>
+          <t>2026-09-15 22:23:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:13</t>
+          <t>2026-09-15 22:23:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:13</t>
+          <t>2026-09-15 22:23:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:13</t>
+          <t>2026-09-15 22:23:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:13</t>
+          <t>2026-09-15 22:23:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:14</t>
+          <t>2026-09-15 22:23:32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:14</t>
+          <t>2026-09-15 22:23:32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:14</t>
+          <t>2026-09-15 22:23:32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:14</t>
+          <t>2026-09-15 22:23:32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:14</t>
+          <t>2026-09-15 22:23:32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-15_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:28</t>
+          <t>2026-09-15 22:29:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:28</t>
+          <t>2026-09-15 22:29:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:28</t>
+          <t>2026-09-15 22:29:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:28</t>
+          <t>2026-09-15 22:29:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:28</t>
+          <t>2026-09-15 22:29:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:28</t>
+          <t>2026-09-15 22:29:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:28</t>
+          <t>2026-09-15 22:29:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:28</t>
+          <t>2026-09-15 22:29:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:28</t>
+          <t>2026-09-15 22:29:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:28</t>
+          <t>2026-09-15 22:29:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:28</t>
+          <t>2026-09-15 22:29:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:28</t>
+          <t>2026-09-15 22:29:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:28</t>
+          <t>2026-09-15 22:29:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:28</t>
+          <t>2026-09-15 22:29:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:28</t>
+          <t>2026-09-15 22:29:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:29</t>
+          <t>2026-09-15 22:29:54</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:29</t>
+          <t>2026-09-15 22:29:54</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:29</t>
+          <t>2026-09-15 22:29:54</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:29</t>
+          <t>2026-09-15 22:29:54</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:29</t>
+          <t>2026-09-15 22:29:54</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:29</t>
+          <t>2026-09-15 22:29:54</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:29</t>
+          <t>2026-09-15 22:29:54</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:29</t>
+          <t>2026-09-15 22:29:54</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:29</t>
+          <t>2026-09-15 22:29:54</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:29</t>
+          <t>2026-09-15 22:29:54</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:29</t>
+          <t>2026-09-15 22:29:54</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:29</t>
+          <t>2026-09-15 22:29:54</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:29</t>
+          <t>2026-09-15 22:29:54</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:29</t>
+          <t>2026-09-15 22:29:54</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:29</t>
+          <t>2026-09-15 22:29:54</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:31</t>
+          <t>2026-09-15 22:29:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:31</t>
+          <t>2026-09-15 22:29:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:31</t>
+          <t>2026-09-15 22:29:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:31</t>
+          <t>2026-09-15 22:29:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:31</t>
+          <t>2026-09-15 22:29:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:31</t>
+          <t>2026-09-15 22:29:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:31</t>
+          <t>2026-09-15 22:29:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:31</t>
+          <t>2026-09-15 22:29:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:31</t>
+          <t>2026-09-15 22:29:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:31</t>
+          <t>2026-09-15 22:29:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:31</t>
+          <t>2026-09-15 22:29:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:31</t>
+          <t>2026-09-15 22:29:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:31</t>
+          <t>2026-09-15 22:29:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:31</t>
+          <t>2026-09-15 22:29:56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:31</t>
+          <t>2026-09-15 22:29:56</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:32</t>
+          <t>2026-09-15 22:29:57</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:32</t>
+          <t>2026-09-15 22:29:57</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:32</t>
+          <t>2026-09-15 22:29:57</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:32</t>
+          <t>2026-09-15 22:29:57</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:32</t>
+          <t>2026-09-15 22:29:57</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
